--- a/data/romance_fraud_time.xlsx
+++ b/data/romance_fraud_time.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\nask.man.ac.uk\home$\Documents\GitHub\netflix_romancefraud\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA12859D-5D45-420E-8904-D4B09489FA76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7B750CD4-EC95-4A54-A9C8-834069E6B859}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{43EE68DE-B5F0-484F-A17E-A9E7DAF0E414}"/>
   </bookViews>
@@ -4661,7 +4661,7 @@
         <v>464</v>
       </c>
       <c r="E64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F64">
         <v>0</v>
@@ -4720,7 +4720,7 @@
         <v>472</v>
       </c>
       <c r="E65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F65">
         <v>0</v>
@@ -4779,7 +4779,7 @@
         <v>505</v>
       </c>
       <c r="E66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F66">
         <v>0</v>
@@ -4838,7 +4838,7 @@
         <v>517</v>
       </c>
       <c r="E67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F67">
         <v>0</v>
@@ -4897,7 +4897,7 @@
         <v>454</v>
       </c>
       <c r="E68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F68">
         <v>0</v>
@@ -4956,7 +4956,7 @@
         <v>508</v>
       </c>
       <c r="E69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F69">
         <v>0</v>
@@ -5015,7 +5015,7 @@
         <v>499</v>
       </c>
       <c r="E70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F70">
         <v>0</v>
@@ -5074,7 +5074,7 @@
         <v>447</v>
       </c>
       <c r="E71">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F71">
         <v>0</v>
@@ -5133,7 +5133,7 @@
         <v>469</v>
       </c>
       <c r="E72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F72">
         <v>0</v>
@@ -5192,7 +5192,7 @@
         <v>465</v>
       </c>
       <c r="E73">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73">
         <v>0</v>
@@ -5251,7 +5251,7 @@
         <v>444</v>
       </c>
       <c r="E74">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F74">
         <v>0</v>
@@ -5310,7 +5310,7 @@
         <v>432</v>
       </c>
       <c r="E75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F75">
         <v>0</v>
@@ -5369,7 +5369,7 @@
         <v>518</v>
       </c>
       <c r="E76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F76">
         <v>0</v>
@@ -5428,7 +5428,7 @@
         <v>616</v>
       </c>
       <c r="E77">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F77">
         <v>0</v>
@@ -5487,7 +5487,7 @@
         <v>640</v>
       </c>
       <c r="E78">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F78">
         <v>0</v>
@@ -5546,7 +5546,7 @@
         <v>605</v>
       </c>
       <c r="E79">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F79">
         <v>1</v>
@@ -5605,7 +5605,7 @@
         <v>623</v>
       </c>
       <c r="E80">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F80">
         <v>1</v>
@@ -5664,7 +5664,7 @@
         <v>705</v>
       </c>
       <c r="E81">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F81">
         <v>1</v>
@@ -5723,7 +5723,7 @@
         <v>626</v>
       </c>
       <c r="E82">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82">
         <v>1</v>
@@ -5782,10 +5782,10 @@
         <v>615</v>
       </c>
       <c r="E83">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F83">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G83">
         <v>0</v>
@@ -5841,10 +5841,10 @@
         <v>654</v>
       </c>
       <c r="E84">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F84">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G84">
         <v>0</v>
@@ -5900,10 +5900,10 @@
         <v>736</v>
       </c>
       <c r="E85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G85">
         <v>0</v>
@@ -5959,10 +5959,10 @@
         <v>901</v>
       </c>
       <c r="E86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G86">
         <v>0</v>
@@ -6018,10 +6018,10 @@
         <v>710</v>
       </c>
       <c r="E87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G87">
         <v>0</v>
@@ -6077,10 +6077,10 @@
         <v>802</v>
       </c>
       <c r="E88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G88">
         <v>0</v>
@@ -6136,10 +6136,10 @@
         <v>758</v>
       </c>
       <c r="E89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G89">
         <v>0</v>
@@ -6195,10 +6195,10 @@
         <v>781</v>
       </c>
       <c r="E90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G90">
         <v>0</v>
@@ -6254,10 +6254,10 @@
         <v>785</v>
       </c>
       <c r="E91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G91">
         <v>0</v>
@@ -6313,10 +6313,10 @@
         <v>680</v>
       </c>
       <c r="E92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G92">
         <v>0</v>
@@ -6372,10 +6372,10 @@
         <v>781</v>
       </c>
       <c r="E93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G93">
         <v>0</v>
@@ -6431,10 +6431,10 @@
         <v>741</v>
       </c>
       <c r="E94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G94">
         <v>0</v>
@@ -6490,10 +6490,10 @@
         <v>660</v>
       </c>
       <c r="E95">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F95">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G95">
         <v>1</v>
@@ -6549,10 +6549,10 @@
         <v>684</v>
       </c>
       <c r="E96">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F96">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G96">
         <v>1</v>
@@ -6608,10 +6608,10 @@
         <v>671</v>
       </c>
       <c r="E97">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F97">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G97">
         <v>1</v>
@@ -6667,10 +6667,10 @@
         <v>583</v>
       </c>
       <c r="E98">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F98">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G98">
         <v>1</v>
@@ -6726,13 +6726,13 @@
         <v>671</v>
       </c>
       <c r="E99">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F99">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G99">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H99">
         <v>1</v>
@@ -6785,16 +6785,16 @@
         <v>767</v>
       </c>
       <c r="E100">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F100">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G100">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H100">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I100">
         <v>1</v>
@@ -6844,19 +6844,19 @@
         <v>668</v>
       </c>
       <c r="E101">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F101">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G101">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H101">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I101">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J101">
         <v>35</v>
@@ -6903,19 +6903,19 @@
         <v>656</v>
       </c>
       <c r="E102">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F102">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G102">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H102">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I102">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J102">
         <v>27</v>
@@ -6962,19 +6962,19 @@
         <v>662</v>
       </c>
       <c r="E103">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F103">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G103">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H103">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I103">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J103">
         <v>24</v>
@@ -7021,19 +7021,19 @@
         <v>662</v>
       </c>
       <c r="E104">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F104">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G104">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H104">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I104">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J104">
         <v>25</v>
@@ -7080,19 +7080,19 @@
         <v>662</v>
       </c>
       <c r="E105">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F105">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G105">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H105">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I105">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J105">
         <v>21</v>
@@ -7139,19 +7139,19 @@
         <v>636</v>
       </c>
       <c r="E106">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F106">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G106">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H106">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I106">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J106">
         <v>23</v>
@@ -7198,19 +7198,19 @@
         <v>616</v>
       </c>
       <c r="E107">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F107">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G107">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H107">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I107">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J107">
         <v>32</v>
@@ -7257,19 +7257,19 @@
         <v>686</v>
       </c>
       <c r="E108">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F108">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G108">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H108">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I108">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J108">
         <v>37</v>
@@ -7316,19 +7316,19 @@
         <v>594</v>
       </c>
       <c r="E109">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F109">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G109">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H109">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I109">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J109">
         <v>47</v>
@@ -7375,19 +7375,19 @@
         <v>774</v>
       </c>
       <c r="E110">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F110">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G110">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H110">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I110">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J110">
         <v>34</v>
@@ -7434,19 +7434,19 @@
         <v>642</v>
       </c>
       <c r="E111">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F111">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G111">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H111">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I111">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J111">
         <v>24</v>
@@ -7493,19 +7493,19 @@
         <v>657</v>
       </c>
       <c r="E112">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F112">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G112">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H112">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I112">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J112">
         <v>30</v>
@@ -7552,19 +7552,19 @@
         <v>756</v>
       </c>
       <c r="E113">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F113">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G113">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H113">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I113">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J113">
         <v>30</v>
@@ -7611,19 +7611,19 @@
         <v>830</v>
       </c>
       <c r="E114">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F114">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G114">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H114">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I114">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J114">
         <v>27</v>
@@ -7670,19 +7670,19 @@
         <v>867</v>
       </c>
       <c r="E115">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F115">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G115">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H115">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I115">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J115">
         <v>31</v>
@@ -7729,19 +7729,19 @@
         <v>686</v>
       </c>
       <c r="E116">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F116">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G116">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H116">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I116">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J116">
         <v>53</v>
@@ -7788,19 +7788,19 @@
         <v>759</v>
       </c>
       <c r="E117">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F117">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G117">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H117">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I117">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J117">
         <v>35</v>
@@ -7847,19 +7847,19 @@
         <v>695</v>
       </c>
       <c r="E118">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F118">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G118">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H118">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I118">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J118">
         <v>39</v>
@@ -7906,19 +7906,19 @@
         <v>662</v>
       </c>
       <c r="E119">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F119">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G119">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H119">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I119">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J119">
         <v>36</v>

--- a/data/romance_fraud_time.xlsx
+++ b/data/romance_fraud_time.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\nask.man.ac.uk\home$\Documents\GitHub\netflix_romancefraud\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7B750CD4-EC95-4A54-A9C8-834069E6B859}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40A22057-CBDD-4042-A184-8723F3060858}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{43EE68DE-B5F0-484F-A17E-A9E7DAF0E414}"/>
+    <workbookView xWindow="7200" yWindow="990" windowWidth="21600" windowHeight="11325" xr2:uid="{43EE68DE-B5F0-484F-A17E-A9E7DAF0E414}"/>
   </bookViews>
   <sheets>
     <sheet name="in" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>Month</t>
   </si>
@@ -82,16 +82,7 @@
     <t xml:space="preserve">Doc Bad Vegan </t>
   </si>
   <si>
-    <t>Dating Scam 1 lag</t>
-  </si>
-  <si>
     <t>Month single</t>
-  </si>
-  <si>
-    <t>Google Trends 1 lag</t>
-  </si>
-  <si>
-    <t>News Articles 1 lag</t>
   </si>
 </sst>
 </file>
@@ -933,72 +924,63 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF9D5820-F434-4204-8EC6-E4855EFF0619}">
-  <dimension ref="A1:S119"/>
+  <dimension ref="A1:P119"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
       </c>
       <c r="D1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I1" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="J1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="L1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M1" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="N1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="P1" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>7</v>
-      </c>
-      <c r="R1" t="s">
-        <v>8</v>
-      </c>
-      <c r="S1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>41730</v>
       </c>
@@ -1008,6 +990,9 @@
       <c r="C2">
         <v>185</v>
       </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
       <c r="E2">
         <v>0</v>
       </c>
@@ -1021,34 +1006,31 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="J2">
-        <v>31</v>
+        <v>2</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2">
-        <v>0</v>
-      </c>
-      <c r="Q2">
-        <v>0</v>
-      </c>
-      <c r="R2">
-        <v>0</v>
-      </c>
-      <c r="S2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>41760</v>
       </c>
@@ -1059,7 +1041,7 @@
         <v>210</v>
       </c>
       <c r="D3">
-        <v>185</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -1074,40 +1056,31 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J3">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
         <v>2</v>
       </c>
-      <c r="N3">
-        <v>1</v>
-      </c>
-      <c r="O3">
-        <v>0</v>
-      </c>
-      <c r="P3">
-        <v>0</v>
-      </c>
-      <c r="Q3">
-        <v>0</v>
-      </c>
-      <c r="R3">
-        <v>0</v>
-      </c>
-      <c r="S3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>41791</v>
       </c>
@@ -1118,7 +1091,7 @@
         <v>199</v>
       </c>
       <c r="D4">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -1133,40 +1106,31 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="J4">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K4">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N4">
         <v>0</v>
       </c>
       <c r="O4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P4">
-        <v>0</v>
-      </c>
-      <c r="Q4">
-        <v>0</v>
-      </c>
-      <c r="R4">
-        <v>0</v>
-      </c>
-      <c r="S4">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>41821</v>
       </c>
@@ -1177,7 +1141,7 @@
         <v>158</v>
       </c>
       <c r="D5">
-        <v>199</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -1192,16 +1156,16 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="J5">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="K5">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="L5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M5">
         <v>0</v>
@@ -1210,22 +1174,13 @@
         <v>0</v>
       </c>
       <c r="O5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>0</v>
-      </c>
-      <c r="Q5">
-        <v>0</v>
-      </c>
-      <c r="R5">
-        <v>0</v>
-      </c>
-      <c r="S5">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>41852</v>
       </c>
@@ -1236,7 +1191,7 @@
         <v>191</v>
       </c>
       <c r="D6">
-        <v>158</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -1251,40 +1206,31 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="J6">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="K6">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="L6">
         <v>1</v>
       </c>
       <c r="M6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N6">
         <v>0</v>
       </c>
       <c r="O6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>0</v>
-      </c>
-      <c r="Q6">
-        <v>0</v>
-      </c>
-      <c r="R6">
-        <v>0</v>
-      </c>
-      <c r="S6">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>41883</v>
       </c>
@@ -1295,7 +1241,7 @@
         <v>215</v>
       </c>
       <c r="D7">
-        <v>191</v>
+        <v>0</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -1310,16 +1256,16 @@
         <v>0</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J7">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="K7">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="L7">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M7">
         <v>1</v>
@@ -1331,19 +1277,10 @@
         <v>0</v>
       </c>
       <c r="P7">
-        <v>1</v>
-      </c>
-      <c r="Q7">
-        <v>0</v>
-      </c>
-      <c r="R7">
-        <v>0</v>
-      </c>
-      <c r="S7">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>41913</v>
       </c>
@@ -1354,7 +1291,7 @@
         <v>229</v>
       </c>
       <c r="D8">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -1369,19 +1306,19 @@
         <v>0</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="J8">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="K8">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="L8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M8">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="N8">
         <v>0</v>
@@ -1390,19 +1327,10 @@
         <v>0</v>
       </c>
       <c r="P8">
-        <v>1</v>
-      </c>
-      <c r="Q8">
-        <v>0</v>
-      </c>
-      <c r="R8">
-        <v>0</v>
-      </c>
-      <c r="S8">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>41944</v>
       </c>
@@ -1413,7 +1341,7 @@
         <v>260</v>
       </c>
       <c r="D9">
-        <v>229</v>
+        <v>0</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -1428,19 +1356,19 @@
         <v>0</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="J9">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="K9">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="L9">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M9">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N9">
         <v>0</v>
@@ -1449,19 +1377,10 @@
         <v>0</v>
       </c>
       <c r="P9">
-        <v>1</v>
-      </c>
-      <c r="Q9">
-        <v>0</v>
-      </c>
-      <c r="R9">
-        <v>0</v>
-      </c>
-      <c r="S9">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>41974</v>
       </c>
@@ -1472,7 +1391,7 @@
         <v>234</v>
       </c>
       <c r="D10">
-        <v>260</v>
+        <v>0</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -1487,40 +1406,31 @@
         <v>0</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J10">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="K10">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="L10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M10">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O10">
         <v>0</v>
       </c>
       <c r="P10">
-        <v>0</v>
-      </c>
-      <c r="Q10">
-        <v>1</v>
-      </c>
-      <c r="R10">
-        <v>0</v>
-      </c>
-      <c r="S10">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>42005</v>
       </c>
@@ -1531,7 +1441,7 @@
         <v>318</v>
       </c>
       <c r="D11">
-        <v>234</v>
+        <v>0</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -1546,40 +1456,31 @@
         <v>0</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="J11">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="K11">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="L11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O11">
         <v>0</v>
       </c>
       <c r="P11">
-        <v>0</v>
-      </c>
-      <c r="Q11">
-        <v>1</v>
-      </c>
-      <c r="R11">
-        <v>0</v>
-      </c>
-      <c r="S11">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>42036</v>
       </c>
@@ -1590,7 +1491,7 @@
         <v>251</v>
       </c>
       <c r="D12">
-        <v>318</v>
+        <v>0</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -1605,40 +1506,31 @@
         <v>0</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J12">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="K12">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="L12">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O12">
         <v>0</v>
       </c>
       <c r="P12">
-        <v>0</v>
-      </c>
-      <c r="Q12">
-        <v>1</v>
-      </c>
-      <c r="R12">
-        <v>0</v>
-      </c>
-      <c r="S12">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>42064</v>
       </c>
@@ -1649,7 +1541,7 @@
         <v>250</v>
       </c>
       <c r="D13">
-        <v>251</v>
+        <v>0</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1664,40 +1556,31 @@
         <v>0</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="J13">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="K13">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="L13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M13">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O13">
         <v>0</v>
       </c>
       <c r="P13">
-        <v>0</v>
-      </c>
-      <c r="Q13">
-        <v>0</v>
-      </c>
-      <c r="R13">
-        <v>0</v>
-      </c>
-      <c r="S13">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>42095</v>
       </c>
@@ -1708,7 +1591,7 @@
         <v>208</v>
       </c>
       <c r="D14">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -1723,40 +1606,31 @@
         <v>0</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="J14">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="K14">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="L14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O14">
         <v>0</v>
       </c>
       <c r="P14">
-        <v>0</v>
-      </c>
-      <c r="Q14">
-        <v>0</v>
-      </c>
-      <c r="R14">
-        <v>0</v>
-      </c>
-      <c r="S14">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>42125</v>
       </c>
@@ -1767,7 +1641,7 @@
         <v>219</v>
       </c>
       <c r="D15">
-        <v>208</v>
+        <v>0</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -1782,40 +1656,31 @@
         <v>0</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="J15">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="K15">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="L15">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O15">
         <v>0</v>
       </c>
       <c r="P15">
-        <v>0</v>
-      </c>
-      <c r="Q15">
-        <v>0</v>
-      </c>
-      <c r="R15">
-        <v>0</v>
-      </c>
-      <c r="S15">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>42156</v>
       </c>
@@ -1826,7 +1691,7 @@
         <v>247</v>
       </c>
       <c r="D16">
-        <v>219</v>
+        <v>0</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -1841,40 +1706,31 @@
         <v>0</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="J16">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="K16">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="L16">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M16">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N16">
         <v>0</v>
       </c>
       <c r="O16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P16">
-        <v>0</v>
-      </c>
-      <c r="Q16">
-        <v>0</v>
-      </c>
-      <c r="R16">
-        <v>0</v>
-      </c>
-      <c r="S16">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>42186</v>
       </c>
@@ -1885,7 +1741,7 @@
         <v>242</v>
       </c>
       <c r="D17">
-        <v>247</v>
+        <v>0</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -1900,40 +1756,31 @@
         <v>0</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="J17">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="K17">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="L17">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M17">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N17">
         <v>0</v>
       </c>
       <c r="O17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P17">
-        <v>0</v>
-      </c>
-      <c r="Q17">
-        <v>0</v>
-      </c>
-      <c r="R17">
-        <v>0</v>
-      </c>
-      <c r="S17">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>42217</v>
       </c>
@@ -1944,7 +1791,7 @@
         <v>206</v>
       </c>
       <c r="D18">
-        <v>242</v>
+        <v>0</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -1959,40 +1806,31 @@
         <v>0</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="J18">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="K18">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="L18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M18">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N18">
         <v>0</v>
       </c>
       <c r="O18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P18">
-        <v>0</v>
-      </c>
-      <c r="Q18">
-        <v>0</v>
-      </c>
-      <c r="R18">
-        <v>0</v>
-      </c>
-      <c r="S18">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>42248</v>
       </c>
@@ -2003,7 +1841,7 @@
         <v>185</v>
       </c>
       <c r="D19">
-        <v>206</v>
+        <v>0</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -2018,19 +1856,19 @@
         <v>0</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="J19">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="K19">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="L19">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N19">
         <v>0</v>
@@ -2039,19 +1877,10 @@
         <v>0</v>
       </c>
       <c r="P19">
-        <v>1</v>
-      </c>
-      <c r="Q19">
-        <v>0</v>
-      </c>
-      <c r="R19">
-        <v>0</v>
-      </c>
-      <c r="S19">
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>42278</v>
       </c>
@@ -2062,7 +1891,7 @@
         <v>177</v>
       </c>
       <c r="D20">
-        <v>185</v>
+        <v>0</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -2077,19 +1906,19 @@
         <v>0</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="J20">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="K20">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="L20">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M20">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N20">
         <v>0</v>
@@ -2098,19 +1927,10 @@
         <v>0</v>
       </c>
       <c r="P20">
-        <v>1</v>
-      </c>
-      <c r="Q20">
-        <v>0</v>
-      </c>
-      <c r="R20">
-        <v>0</v>
-      </c>
-      <c r="S20">
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>42309</v>
       </c>
@@ -2121,7 +1941,7 @@
         <v>174</v>
       </c>
       <c r="D21">
-        <v>177</v>
+        <v>0</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -2136,19 +1956,19 @@
         <v>0</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="J21">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="K21">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="L21">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M21">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="N21">
         <v>0</v>
@@ -2157,19 +1977,10 @@
         <v>0</v>
       </c>
       <c r="P21">
-        <v>1</v>
-      </c>
-      <c r="Q21">
-        <v>0</v>
-      </c>
-      <c r="R21">
-        <v>0</v>
-      </c>
-      <c r="S21">
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>42339</v>
       </c>
@@ -2180,7 +1991,7 @@
         <v>218</v>
       </c>
       <c r="D22">
-        <v>174</v>
+        <v>0</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -2195,40 +2006,31 @@
         <v>0</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J22">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="K22">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="L22">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M22">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O22">
         <v>0</v>
       </c>
       <c r="P22">
-        <v>0</v>
-      </c>
-      <c r="Q22">
-        <v>1</v>
-      </c>
-      <c r="R22">
-        <v>0</v>
-      </c>
-      <c r="S22">
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>42370</v>
       </c>
@@ -2239,7 +2041,7 @@
         <v>207</v>
       </c>
       <c r="D23">
-        <v>218</v>
+        <v>0</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -2254,40 +2056,31 @@
         <v>0</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="J23">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="K23">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="L23">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M23">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O23">
         <v>0</v>
       </c>
       <c r="P23">
-        <v>0</v>
-      </c>
-      <c r="Q23">
-        <v>1</v>
-      </c>
-      <c r="R23">
-        <v>0</v>
-      </c>
-      <c r="S23">
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>42401</v>
       </c>
@@ -2298,7 +2091,7 @@
         <v>227</v>
       </c>
       <c r="D24">
-        <v>207</v>
+        <v>0</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -2313,40 +2106,31 @@
         <v>0</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J24">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="K24">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="L24">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="M24">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O24">
         <v>0</v>
       </c>
       <c r="P24">
-        <v>0</v>
-      </c>
-      <c r="Q24">
-        <v>1</v>
-      </c>
-      <c r="R24">
-        <v>0</v>
-      </c>
-      <c r="S24">
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>42430</v>
       </c>
@@ -2357,7 +2141,7 @@
         <v>253</v>
       </c>
       <c r="D25">
-        <v>227</v>
+        <v>0</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -2372,40 +2156,31 @@
         <v>0</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="J25">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="K25">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="L25">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M25">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="N25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O25">
         <v>0</v>
       </c>
       <c r="P25">
-        <v>0</v>
-      </c>
-      <c r="Q25">
-        <v>0</v>
-      </c>
-      <c r="R25">
-        <v>0</v>
-      </c>
-      <c r="S25">
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>42461</v>
       </c>
@@ -2416,7 +2191,7 @@
         <v>242</v>
       </c>
       <c r="D26">
-        <v>253</v>
+        <v>0</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -2431,40 +2206,31 @@
         <v>0</v>
       </c>
       <c r="I26">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="J26">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="K26">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="L26">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M26">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O26">
         <v>0</v>
       </c>
       <c r="P26">
-        <v>0</v>
-      </c>
-      <c r="Q26">
-        <v>0</v>
-      </c>
-      <c r="R26">
-        <v>0</v>
-      </c>
-      <c r="S26">
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>42491</v>
       </c>
@@ -2475,7 +2241,7 @@
         <v>231</v>
       </c>
       <c r="D27">
-        <v>242</v>
+        <v>0</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -2490,40 +2256,31 @@
         <v>0</v>
       </c>
       <c r="I27">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="J27">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="K27">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="L27">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M27">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O27">
         <v>0</v>
       </c>
       <c r="P27">
-        <v>0</v>
-      </c>
-      <c r="Q27">
-        <v>0</v>
-      </c>
-      <c r="R27">
-        <v>0</v>
-      </c>
-      <c r="S27">
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>42522</v>
       </c>
@@ -2534,7 +2291,7 @@
         <v>276</v>
       </c>
       <c r="D28">
-        <v>231</v>
+        <v>0</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -2549,40 +2306,31 @@
         <v>0</v>
       </c>
       <c r="I28">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="J28">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="K28">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="L28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M28">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N28">
         <v>0</v>
       </c>
       <c r="O28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P28">
-        <v>0</v>
-      </c>
-      <c r="Q28">
-        <v>0</v>
-      </c>
-      <c r="R28">
-        <v>0</v>
-      </c>
-      <c r="S28">
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>42552</v>
       </c>
@@ -2593,7 +2341,7 @@
         <v>268</v>
       </c>
       <c r="D29">
-        <v>276</v>
+        <v>0</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -2608,40 +2356,31 @@
         <v>0</v>
       </c>
       <c r="I29">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J29">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K29">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M29">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N29">
         <v>0</v>
       </c>
       <c r="O29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P29">
-        <v>0</v>
-      </c>
-      <c r="Q29">
-        <v>0</v>
-      </c>
-      <c r="R29">
-        <v>0</v>
-      </c>
-      <c r="S29">
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>42583</v>
       </c>
@@ -2652,7 +2391,7 @@
         <v>275</v>
       </c>
       <c r="D30">
-        <v>268</v>
+        <v>0</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -2667,13 +2406,13 @@
         <v>0</v>
       </c>
       <c r="I30">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="J30">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="K30">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="L30">
         <v>1</v>
@@ -2685,22 +2424,13 @@
         <v>0</v>
       </c>
       <c r="O30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P30">
-        <v>0</v>
-      </c>
-      <c r="Q30">
-        <v>0</v>
-      </c>
-      <c r="R30">
-        <v>0</v>
-      </c>
-      <c r="S30">
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>42614</v>
       </c>
@@ -2711,7 +2441,7 @@
         <v>264</v>
       </c>
       <c r="D31">
-        <v>275</v>
+        <v>0</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -2726,16 +2456,16 @@
         <v>0</v>
       </c>
       <c r="I31">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="J31">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="K31">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="L31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M31">
         <v>1</v>
@@ -2747,19 +2477,10 @@
         <v>0</v>
       </c>
       <c r="P31">
-        <v>1</v>
-      </c>
-      <c r="Q31">
-        <v>0</v>
-      </c>
-      <c r="R31">
-        <v>0</v>
-      </c>
-      <c r="S31">
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>42644</v>
       </c>
@@ -2770,7 +2491,7 @@
         <v>274</v>
       </c>
       <c r="D32">
-        <v>264</v>
+        <v>0</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -2785,16 +2506,16 @@
         <v>0</v>
       </c>
       <c r="I32">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J32">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="K32">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="L32">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M32">
         <v>1</v>
@@ -2806,19 +2527,10 @@
         <v>0</v>
       </c>
       <c r="P32">
-        <v>1</v>
-      </c>
-      <c r="Q32">
-        <v>0</v>
-      </c>
-      <c r="R32">
-        <v>0</v>
-      </c>
-      <c r="S32">
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>42675</v>
       </c>
@@ -2829,7 +2541,7 @@
         <v>291</v>
       </c>
       <c r="D33">
-        <v>274</v>
+        <v>0</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -2844,19 +2556,19 @@
         <v>0</v>
       </c>
       <c r="I33">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="J33">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="K33">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="L33">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M33">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N33">
         <v>0</v>
@@ -2865,19 +2577,10 @@
         <v>0</v>
       </c>
       <c r="P33">
-        <v>1</v>
-      </c>
-      <c r="Q33">
-        <v>0</v>
-      </c>
-      <c r="R33">
-        <v>0</v>
-      </c>
-      <c r="S33">
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>42705</v>
       </c>
@@ -2888,7 +2591,7 @@
         <v>233</v>
       </c>
       <c r="D34">
-        <v>291</v>
+        <v>0</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -2903,40 +2606,31 @@
         <v>0</v>
       </c>
       <c r="I34">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="J34">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="K34">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="L34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M34">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O34">
         <v>0</v>
       </c>
       <c r="P34">
-        <v>0</v>
-      </c>
-      <c r="Q34">
-        <v>1</v>
-      </c>
-      <c r="R34">
-        <v>0</v>
-      </c>
-      <c r="S34">
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>42736</v>
       </c>
@@ -2947,7 +2641,7 @@
         <v>254</v>
       </c>
       <c r="D35">
-        <v>233</v>
+        <v>0</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -2962,40 +2656,31 @@
         <v>0</v>
       </c>
       <c r="I35">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="J35">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="K35">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="L35">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O35">
         <v>0</v>
       </c>
       <c r="P35">
-        <v>0</v>
-      </c>
-      <c r="Q35">
-        <v>1</v>
-      </c>
-      <c r="R35">
-        <v>0</v>
-      </c>
-      <c r="S35">
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>42767</v>
       </c>
@@ -3006,7 +2691,7 @@
         <v>254</v>
       </c>
       <c r="D36">
-        <v>254</v>
+        <v>0</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -3021,40 +2706,31 @@
         <v>0</v>
       </c>
       <c r="I36">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="J36">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="K36">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="L36">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="M36">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O36">
         <v>0</v>
       </c>
       <c r="P36">
-        <v>0</v>
-      </c>
-      <c r="Q36">
-        <v>1</v>
-      </c>
-      <c r="R36">
-        <v>0</v>
-      </c>
-      <c r="S36">
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>42795</v>
       </c>
@@ -3065,7 +2741,7 @@
         <v>277</v>
       </c>
       <c r="D37">
-        <v>254</v>
+        <v>0</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -3080,40 +2756,31 @@
         <v>0</v>
       </c>
       <c r="I37">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="J37">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="K37">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="L37">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="M37">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="N37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O37">
         <v>0</v>
       </c>
       <c r="P37">
-        <v>0</v>
-      </c>
-      <c r="Q37">
-        <v>0</v>
-      </c>
-      <c r="R37">
-        <v>0</v>
-      </c>
-      <c r="S37">
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>42826</v>
       </c>
@@ -3124,7 +2791,7 @@
         <v>288</v>
       </c>
       <c r="D38">
-        <v>277</v>
+        <v>0</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -3139,40 +2806,31 @@
         <v>0</v>
       </c>
       <c r="I38">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J38">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="K38">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="L38">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M38">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="N38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O38">
         <v>0</v>
       </c>
       <c r="P38">
-        <v>0</v>
-      </c>
-      <c r="Q38">
-        <v>0</v>
-      </c>
-      <c r="R38">
-        <v>0</v>
-      </c>
-      <c r="S38">
         <v>37</v>
       </c>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>42856</v>
       </c>
@@ -3183,7 +2841,7 @@
         <v>291</v>
       </c>
       <c r="D39">
-        <v>288</v>
+        <v>0</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -3198,40 +2856,31 @@
         <v>0</v>
       </c>
       <c r="I39">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J39">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="K39">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="L39">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M39">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O39">
         <v>0</v>
       </c>
       <c r="P39">
-        <v>0</v>
-      </c>
-      <c r="Q39">
-        <v>0</v>
-      </c>
-      <c r="R39">
-        <v>0</v>
-      </c>
-      <c r="S39">
         <v>38</v>
       </c>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>42887</v>
       </c>
@@ -3242,7 +2891,7 @@
         <v>277</v>
       </c>
       <c r="D40">
-        <v>291</v>
+        <v>0</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -3257,40 +2906,31 @@
         <v>0</v>
       </c>
       <c r="I40">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="J40">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="K40">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="L40">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="M40">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N40">
         <v>0</v>
       </c>
       <c r="O40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P40">
-        <v>0</v>
-      </c>
-      <c r="Q40">
-        <v>0</v>
-      </c>
-      <c r="R40">
-        <v>0</v>
-      </c>
-      <c r="S40">
         <v>39</v>
       </c>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>42917</v>
       </c>
@@ -3301,7 +2941,7 @@
         <v>313</v>
       </c>
       <c r="D41">
-        <v>277</v>
+        <v>0</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -3316,40 +2956,31 @@
         <v>0</v>
       </c>
       <c r="I41">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="J41">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="K41">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="L41">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M41">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N41">
         <v>0</v>
       </c>
       <c r="O41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P41">
-        <v>0</v>
-      </c>
-      <c r="Q41">
-        <v>0</v>
-      </c>
-      <c r="R41">
-        <v>0</v>
-      </c>
-      <c r="S41">
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>42948</v>
       </c>
@@ -3360,7 +2991,7 @@
         <v>325</v>
       </c>
       <c r="D42">
-        <v>313</v>
+        <v>0</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -3375,40 +3006,31 @@
         <v>0</v>
       </c>
       <c r="I42">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="J42">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="K42">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="L42">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M42">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N42">
         <v>0</v>
       </c>
       <c r="O42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P42">
-        <v>0</v>
-      </c>
-      <c r="Q42">
-        <v>0</v>
-      </c>
-      <c r="R42">
-        <v>0</v>
-      </c>
-      <c r="S42">
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>42979</v>
       </c>
@@ -3419,7 +3041,7 @@
         <v>293</v>
       </c>
       <c r="D43">
-        <v>325</v>
+        <v>0</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -3434,19 +3056,19 @@
         <v>0</v>
       </c>
       <c r="I43">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J43">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="K43">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="L43">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M43">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N43">
         <v>0</v>
@@ -3455,19 +3077,10 @@
         <v>0</v>
       </c>
       <c r="P43">
-        <v>1</v>
-      </c>
-      <c r="Q43">
-        <v>0</v>
-      </c>
-      <c r="R43">
-        <v>0</v>
-      </c>
-      <c r="S43">
         <v>42</v>
       </c>
     </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>43009</v>
       </c>
@@ -3478,7 +3091,7 @@
         <v>366</v>
       </c>
       <c r="D44">
-        <v>293</v>
+        <v>0</v>
       </c>
       <c r="E44">
         <v>0</v>
@@ -3493,19 +3106,19 @@
         <v>0</v>
       </c>
       <c r="I44">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J44">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="K44">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="L44">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N44">
         <v>0</v>
@@ -3514,19 +3127,10 @@
         <v>0</v>
       </c>
       <c r="P44">
-        <v>1</v>
-      </c>
-      <c r="Q44">
-        <v>0</v>
-      </c>
-      <c r="R44">
-        <v>0</v>
-      </c>
-      <c r="S44">
         <v>43</v>
       </c>
     </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>43040</v>
       </c>
@@ -3537,7 +3141,7 @@
         <v>342</v>
       </c>
       <c r="D45">
-        <v>366</v>
+        <v>0</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -3552,19 +3156,19 @@
         <v>0</v>
       </c>
       <c r="I45">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J45">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K45">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="L45">
         <v>0</v>
       </c>
       <c r="M45">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="N45">
         <v>0</v>
@@ -3573,19 +3177,10 @@
         <v>0</v>
       </c>
       <c r="P45">
-        <v>1</v>
-      </c>
-      <c r="Q45">
-        <v>0</v>
-      </c>
-      <c r="R45">
-        <v>0</v>
-      </c>
-      <c r="S45">
         <v>44</v>
       </c>
     </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>43070</v>
       </c>
@@ -3596,7 +3191,7 @@
         <v>377</v>
       </c>
       <c r="D46">
-        <v>342</v>
+        <v>0</v>
       </c>
       <c r="E46">
         <v>0</v>
@@ -3611,40 +3206,31 @@
         <v>0</v>
       </c>
       <c r="I46">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="J46">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="K46">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="L46">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M46">
         <v>0</v>
       </c>
       <c r="N46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O46">
         <v>0</v>
       </c>
       <c r="P46">
-        <v>0</v>
-      </c>
-      <c r="Q46">
-        <v>1</v>
-      </c>
-      <c r="R46">
-        <v>0</v>
-      </c>
-      <c r="S46">
         <v>45</v>
       </c>
     </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>43101</v>
       </c>
@@ -3655,7 +3241,7 @@
         <v>347</v>
       </c>
       <c r="D47">
-        <v>377</v>
+        <v>0</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -3670,40 +3256,31 @@
         <v>0</v>
       </c>
       <c r="I47">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="J47">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="K47">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="L47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M47">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O47">
         <v>0</v>
       </c>
       <c r="P47">
-        <v>0</v>
-      </c>
-      <c r="Q47">
-        <v>1</v>
-      </c>
-      <c r="R47">
-        <v>0</v>
-      </c>
-      <c r="S47">
         <v>46</v>
       </c>
     </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>43132</v>
       </c>
@@ -3714,7 +3291,7 @@
         <v>333</v>
       </c>
       <c r="D48">
-        <v>347</v>
+        <v>0</v>
       </c>
       <c r="E48">
         <v>0</v>
@@ -3729,40 +3306,31 @@
         <v>0</v>
       </c>
       <c r="I48">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J48">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K48">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="L48">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="M48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O48">
         <v>0</v>
       </c>
       <c r="P48">
-        <v>0</v>
-      </c>
-      <c r="Q48">
-        <v>1</v>
-      </c>
-      <c r="R48">
-        <v>0</v>
-      </c>
-      <c r="S48">
         <v>47</v>
       </c>
     </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>43160</v>
       </c>
@@ -3773,7 +3341,7 @@
         <v>325</v>
       </c>
       <c r="D49">
-        <v>333</v>
+        <v>0</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -3788,40 +3356,31 @@
         <v>0</v>
       </c>
       <c r="I49">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="J49">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="K49">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="L49">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M49">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="N49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O49">
         <v>0</v>
       </c>
       <c r="P49">
-        <v>0</v>
-      </c>
-      <c r="Q49">
-        <v>0</v>
-      </c>
-      <c r="R49">
-        <v>0</v>
-      </c>
-      <c r="S49">
         <v>48</v>
       </c>
     </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>43191</v>
       </c>
@@ -3832,7 +3391,7 @@
         <v>335</v>
       </c>
       <c r="D50">
-        <v>325</v>
+        <v>0</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -3847,40 +3406,31 @@
         <v>0</v>
       </c>
       <c r="I50">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="J50">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="K50">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="L50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M50">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O50">
         <v>0</v>
       </c>
       <c r="P50">
-        <v>0</v>
-      </c>
-      <c r="Q50">
-        <v>0</v>
-      </c>
-      <c r="R50">
-        <v>0</v>
-      </c>
-      <c r="S50">
         <v>49</v>
       </c>
     </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>43221</v>
       </c>
@@ -3891,7 +3441,7 @@
         <v>356</v>
       </c>
       <c r="D51">
-        <v>335</v>
+        <v>0</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -3906,40 +3456,31 @@
         <v>0</v>
       </c>
       <c r="I51">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="J51">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="K51">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="L51">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O51">
         <v>0</v>
       </c>
       <c r="P51">
-        <v>0</v>
-      </c>
-      <c r="Q51">
-        <v>0</v>
-      </c>
-      <c r="R51">
-        <v>0</v>
-      </c>
-      <c r="S51">
         <v>50</v>
       </c>
     </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>43252</v>
       </c>
@@ -3950,7 +3491,7 @@
         <v>335</v>
       </c>
       <c r="D52">
-        <v>356</v>
+        <v>0</v>
       </c>
       <c r="E52">
         <v>0</v>
@@ -3965,40 +3506,31 @@
         <v>0</v>
       </c>
       <c r="I52">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="J52">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="K52">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="L52">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M52">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N52">
         <v>0</v>
       </c>
       <c r="O52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P52">
-        <v>0</v>
-      </c>
-      <c r="Q52">
-        <v>0</v>
-      </c>
-      <c r="R52">
-        <v>0</v>
-      </c>
-      <c r="S52">
         <v>51</v>
       </c>
     </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>43282</v>
       </c>
@@ -4009,7 +3541,7 @@
         <v>315</v>
       </c>
       <c r="D53">
-        <v>335</v>
+        <v>0</v>
       </c>
       <c r="E53">
         <v>0</v>
@@ -4024,40 +3556,31 @@
         <v>0</v>
       </c>
       <c r="I53">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J53">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="K53">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="L53">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="M53">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N53">
         <v>0</v>
       </c>
       <c r="O53">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P53">
-        <v>0</v>
-      </c>
-      <c r="Q53">
-        <v>0</v>
-      </c>
-      <c r="R53">
-        <v>0</v>
-      </c>
-      <c r="S53">
         <v>52</v>
       </c>
     </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>43313</v>
       </c>
@@ -4068,7 +3591,7 @@
         <v>414</v>
       </c>
       <c r="D54">
-        <v>315</v>
+        <v>0</v>
       </c>
       <c r="E54">
         <v>0</v>
@@ -4083,40 +3606,31 @@
         <v>0</v>
       </c>
       <c r="I54">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J54">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="K54">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="L54">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M54">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N54">
         <v>0</v>
       </c>
       <c r="O54">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P54">
-        <v>0</v>
-      </c>
-      <c r="Q54">
-        <v>0</v>
-      </c>
-      <c r="R54">
-        <v>0</v>
-      </c>
-      <c r="S54">
         <v>53</v>
       </c>
     </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>43344</v>
       </c>
@@ -4127,7 +3641,7 @@
         <v>362</v>
       </c>
       <c r="D55">
-        <v>414</v>
+        <v>0</v>
       </c>
       <c r="E55">
         <v>0</v>
@@ -4142,19 +3656,19 @@
         <v>0</v>
       </c>
       <c r="I55">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="J55">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K55">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="L55">
         <v>0</v>
       </c>
       <c r="M55">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N55">
         <v>0</v>
@@ -4163,19 +3677,10 @@
         <v>0</v>
       </c>
       <c r="P55">
-        <v>1</v>
-      </c>
-      <c r="Q55">
-        <v>0</v>
-      </c>
-      <c r="R55">
-        <v>0</v>
-      </c>
-      <c r="S55">
         <v>54</v>
       </c>
     </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>43374</v>
       </c>
@@ -4186,7 +3691,7 @@
         <v>473</v>
       </c>
       <c r="D56">
-        <v>362</v>
+        <v>0</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -4201,19 +3706,19 @@
         <v>0</v>
       </c>
       <c r="I56">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="J56">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="K56">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="L56">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N56">
         <v>0</v>
@@ -4222,19 +3727,10 @@
         <v>0</v>
       </c>
       <c r="P56">
-        <v>1</v>
-      </c>
-      <c r="Q56">
-        <v>0</v>
-      </c>
-      <c r="R56">
-        <v>0</v>
-      </c>
-      <c r="S56">
         <v>55</v>
       </c>
     </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>43405</v>
       </c>
@@ -4245,7 +3741,7 @@
         <v>480</v>
       </c>
       <c r="D57">
-        <v>473</v>
+        <v>0</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -4260,19 +3756,19 @@
         <v>0</v>
       </c>
       <c r="I57">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="J57">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K57">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="L57">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="M57">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N57">
         <v>0</v>
@@ -4281,19 +3777,10 @@
         <v>0</v>
       </c>
       <c r="P57">
-        <v>1</v>
-      </c>
-      <c r="Q57">
-        <v>0</v>
-      </c>
-      <c r="R57">
-        <v>0</v>
-      </c>
-      <c r="S57">
         <v>56</v>
       </c>
     </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>43435</v>
       </c>
@@ -4304,7 +3791,7 @@
         <v>401</v>
       </c>
       <c r="D58">
-        <v>480</v>
+        <v>0</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -4319,40 +3806,31 @@
         <v>0</v>
       </c>
       <c r="I58">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J58">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="K58">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="L58">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M58">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N58">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O58">
         <v>0</v>
       </c>
       <c r="P58">
-        <v>0</v>
-      </c>
-      <c r="Q58">
-        <v>1</v>
-      </c>
-      <c r="R58">
-        <v>0</v>
-      </c>
-      <c r="S58">
         <v>57</v>
       </c>
     </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>43466</v>
       </c>
@@ -4363,7 +3841,7 @@
         <v>471</v>
       </c>
       <c r="D59">
-        <v>401</v>
+        <v>0</v>
       </c>
       <c r="E59">
         <v>0</v>
@@ -4378,40 +3856,31 @@
         <v>0</v>
       </c>
       <c r="I59">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J59">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="K59">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="L59">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M59">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O59">
         <v>0</v>
       </c>
       <c r="P59">
-        <v>0</v>
-      </c>
-      <c r="Q59">
-        <v>1</v>
-      </c>
-      <c r="R59">
-        <v>0</v>
-      </c>
-      <c r="S59">
         <v>58</v>
       </c>
     </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>43497</v>
       </c>
@@ -4422,10 +3891,10 @@
         <v>443</v>
       </c>
       <c r="D60">
-        <v>471</v>
+        <v>1</v>
       </c>
       <c r="E60">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F60">
         <v>0</v>
@@ -4437,40 +3906,31 @@
         <v>0</v>
       </c>
       <c r="I60">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="J60">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="K60">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="L60">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="M60">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O60">
         <v>0</v>
       </c>
       <c r="P60">
-        <v>0</v>
-      </c>
-      <c r="Q60">
-        <v>1</v>
-      </c>
-      <c r="R60">
-        <v>0</v>
-      </c>
-      <c r="S60">
         <v>59</v>
       </c>
     </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>43525</v>
       </c>
@@ -4481,10 +3941,10 @@
         <v>468</v>
       </c>
       <c r="D61">
-        <v>443</v>
+        <v>1</v>
       </c>
       <c r="E61">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F61">
         <v>0</v>
@@ -4496,40 +3956,31 @@
         <v>0</v>
       </c>
       <c r="I61">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="J61">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="K61">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="L61">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M61">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="N61">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O61">
         <v>0</v>
       </c>
       <c r="P61">
-        <v>0</v>
-      </c>
-      <c r="Q61">
-        <v>0</v>
-      </c>
-      <c r="R61">
-        <v>0</v>
-      </c>
-      <c r="S61">
         <v>60</v>
       </c>
     </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>43556</v>
       </c>
@@ -4540,10 +3991,10 @@
         <v>483</v>
       </c>
       <c r="D62">
-        <v>468</v>
+        <v>1</v>
       </c>
       <c r="E62">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F62">
         <v>0</v>
@@ -4555,40 +4006,31 @@
         <v>0</v>
       </c>
       <c r="I62">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J62">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="K62">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="L62">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M62">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N62">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O62">
         <v>0</v>
       </c>
       <c r="P62">
-        <v>0</v>
-      </c>
-      <c r="Q62">
-        <v>0</v>
-      </c>
-      <c r="R62">
-        <v>0</v>
-      </c>
-      <c r="S62">
         <v>61</v>
       </c>
     </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>43586</v>
       </c>
@@ -4599,10 +4041,10 @@
         <v>464</v>
       </c>
       <c r="D63">
-        <v>483</v>
+        <v>1</v>
       </c>
       <c r="E63">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F63">
         <v>0</v>
@@ -4614,40 +4056,31 @@
         <v>0</v>
       </c>
       <c r="I63">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="J63">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="K63">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="L63">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M63">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N63">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O63">
         <v>0</v>
       </c>
       <c r="P63">
-        <v>0</v>
-      </c>
-      <c r="Q63">
-        <v>0</v>
-      </c>
-      <c r="R63">
-        <v>0</v>
-      </c>
-      <c r="S63">
         <v>62</v>
       </c>
     </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>43617</v>
       </c>
@@ -4658,10 +4091,10 @@
         <v>472</v>
       </c>
       <c r="D64">
-        <v>464</v>
+        <v>1</v>
       </c>
       <c r="E64">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F64">
         <v>0</v>
@@ -4673,40 +4106,31 @@
         <v>0</v>
       </c>
       <c r="I64">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="J64">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="K64">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="L64">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="M64">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N64">
         <v>0</v>
       </c>
       <c r="O64">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P64">
-        <v>0</v>
-      </c>
-      <c r="Q64">
-        <v>0</v>
-      </c>
-      <c r="R64">
-        <v>0</v>
-      </c>
-      <c r="S64">
         <v>63</v>
       </c>
     </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>43647</v>
       </c>
@@ -4717,10 +4141,10 @@
         <v>505</v>
       </c>
       <c r="D65">
-        <v>472</v>
+        <v>1</v>
       </c>
       <c r="E65">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F65">
         <v>0</v>
@@ -4732,40 +4156,31 @@
         <v>0</v>
       </c>
       <c r="I65">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J65">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="K65">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="L65">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="M65">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="N65">
         <v>0</v>
       </c>
       <c r="O65">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P65">
-        <v>0</v>
-      </c>
-      <c r="Q65">
-        <v>0</v>
-      </c>
-      <c r="R65">
-        <v>0</v>
-      </c>
-      <c r="S65">
         <v>64</v>
       </c>
     </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>43678</v>
       </c>
@@ -4776,10 +4191,10 @@
         <v>517</v>
       </c>
       <c r="D66">
-        <v>505</v>
+        <v>1</v>
       </c>
       <c r="E66">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F66">
         <v>0</v>
@@ -4791,40 +4206,31 @@
         <v>0</v>
       </c>
       <c r="I66">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="J66">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="K66">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L66">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="M66">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="N66">
         <v>0</v>
       </c>
       <c r="O66">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P66">
-        <v>0</v>
-      </c>
-      <c r="Q66">
-        <v>0</v>
-      </c>
-      <c r="R66">
-        <v>0</v>
-      </c>
-      <c r="S66">
         <v>65</v>
       </c>
     </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>43709</v>
       </c>
@@ -4835,10 +4241,10 @@
         <v>454</v>
       </c>
       <c r="D67">
-        <v>517</v>
+        <v>1</v>
       </c>
       <c r="E67">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F67">
         <v>0</v>
@@ -4850,19 +4256,19 @@
         <v>0</v>
       </c>
       <c r="I67">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="J67">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="K67">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L67">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M67">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="N67">
         <v>0</v>
@@ -4871,19 +4277,10 @@
         <v>0</v>
       </c>
       <c r="P67">
-        <v>1</v>
-      </c>
-      <c r="Q67">
-        <v>0</v>
-      </c>
-      <c r="R67">
-        <v>0</v>
-      </c>
-      <c r="S67">
         <v>66</v>
       </c>
     </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>43739</v>
       </c>
@@ -4894,10 +4291,10 @@
         <v>508</v>
       </c>
       <c r="D68">
-        <v>454</v>
+        <v>1</v>
       </c>
       <c r="E68">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F68">
         <v>0</v>
@@ -4909,19 +4306,19 @@
         <v>0</v>
       </c>
       <c r="I68">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J68">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="K68">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="L68">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M68">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N68">
         <v>0</v>
@@ -4930,19 +4327,10 @@
         <v>0</v>
       </c>
       <c r="P68">
-        <v>1</v>
-      </c>
-      <c r="Q68">
-        <v>0</v>
-      </c>
-      <c r="R68">
-        <v>0</v>
-      </c>
-      <c r="S68">
         <v>67</v>
       </c>
     </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>43770</v>
       </c>
@@ -4953,10 +4341,10 @@
         <v>499</v>
       </c>
       <c r="D69">
-        <v>508</v>
+        <v>1</v>
       </c>
       <c r="E69">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F69">
         <v>0</v>
@@ -4968,19 +4356,19 @@
         <v>0</v>
       </c>
       <c r="I69">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J69">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="K69">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="L69">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M69">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="N69">
         <v>0</v>
@@ -4989,19 +4377,10 @@
         <v>0</v>
       </c>
       <c r="P69">
-        <v>1</v>
-      </c>
-      <c r="Q69">
-        <v>0</v>
-      </c>
-      <c r="R69">
-        <v>0</v>
-      </c>
-      <c r="S69">
         <v>68</v>
       </c>
     </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>43800</v>
       </c>
@@ -5012,10 +4391,10 @@
         <v>447</v>
       </c>
       <c r="D70">
-        <v>499</v>
+        <v>1</v>
       </c>
       <c r="E70">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F70">
         <v>0</v>
@@ -5027,40 +4406,31 @@
         <v>0</v>
       </c>
       <c r="I70">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="J70">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="K70">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="L70">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M70">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O70">
         <v>0</v>
       </c>
       <c r="P70">
-        <v>0</v>
-      </c>
-      <c r="Q70">
-        <v>1</v>
-      </c>
-      <c r="R70">
-        <v>0</v>
-      </c>
-      <c r="S70">
         <v>69</v>
       </c>
     </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>43831</v>
       </c>
@@ -5071,10 +4441,10 @@
         <v>469</v>
       </c>
       <c r="D71">
-        <v>447</v>
+        <v>1</v>
       </c>
       <c r="E71">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F71">
         <v>0</v>
@@ -5086,40 +4456,31 @@
         <v>0</v>
       </c>
       <c r="I71">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J71">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="K71">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="L71">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M71">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N71">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O71">
         <v>0</v>
       </c>
       <c r="P71">
-        <v>0</v>
-      </c>
-      <c r="Q71">
-        <v>1</v>
-      </c>
-      <c r="R71">
-        <v>0</v>
-      </c>
-      <c r="S71">
         <v>70</v>
       </c>
     </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>43862</v>
       </c>
@@ -5130,10 +4491,10 @@
         <v>465</v>
       </c>
       <c r="D72">
-        <v>469</v>
+        <v>1</v>
       </c>
       <c r="E72">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F72">
         <v>0</v>
@@ -5145,40 +4506,31 @@
         <v>0</v>
       </c>
       <c r="I72">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="J72">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="K72">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="L72">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="M72">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="N72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O72">
         <v>0</v>
       </c>
       <c r="P72">
-        <v>0</v>
-      </c>
-      <c r="Q72">
-        <v>1</v>
-      </c>
-      <c r="R72">
-        <v>0</v>
-      </c>
-      <c r="S72">
         <v>71</v>
       </c>
     </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>43891</v>
       </c>
@@ -5189,10 +4541,10 @@
         <v>444</v>
       </c>
       <c r="D73">
-        <v>465</v>
+        <v>1</v>
       </c>
       <c r="E73">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F73">
         <v>0</v>
@@ -5204,40 +4556,31 @@
         <v>0</v>
       </c>
       <c r="I73">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="J73">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="K73">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="L73">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="M73">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N73">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O73">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P73">
-        <v>0</v>
-      </c>
-      <c r="Q73">
-        <v>0</v>
-      </c>
-      <c r="R73">
-        <v>1</v>
-      </c>
-      <c r="S73">
         <v>72</v>
       </c>
     </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>43922</v>
       </c>
@@ -5248,10 +4591,10 @@
         <v>432</v>
       </c>
       <c r="D74">
-        <v>444</v>
+        <v>1</v>
       </c>
       <c r="E74">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F74">
         <v>0</v>
@@ -5263,40 +4606,31 @@
         <v>0</v>
       </c>
       <c r="I74">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="J74">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="K74">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="L74">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M74">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="N74">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O74">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P74">
-        <v>0</v>
-      </c>
-      <c r="Q74">
-        <v>0</v>
-      </c>
-      <c r="R74">
-        <v>1</v>
-      </c>
-      <c r="S74">
         <v>73</v>
       </c>
     </row>
-    <row r="75" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>43952</v>
       </c>
@@ -5307,10 +4641,10 @@
         <v>518</v>
       </c>
       <c r="D75">
-        <v>432</v>
+        <v>1</v>
       </c>
       <c r="E75">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F75">
         <v>0</v>
@@ -5322,40 +4656,31 @@
         <v>0</v>
       </c>
       <c r="I75">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="J75">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="K75">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="L75">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="M75">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N75">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P75">
-        <v>0</v>
-      </c>
-      <c r="Q75">
-        <v>0</v>
-      </c>
-      <c r="R75">
-        <v>1</v>
-      </c>
-      <c r="S75">
         <v>74</v>
       </c>
     </row>
-    <row r="76" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>43983</v>
       </c>
@@ -5366,10 +4691,10 @@
         <v>616</v>
       </c>
       <c r="D76">
-        <v>518</v>
+        <v>1</v>
       </c>
       <c r="E76">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F76">
         <v>0</v>
@@ -5381,19 +4706,19 @@
         <v>0</v>
       </c>
       <c r="I76">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="J76">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="K76">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="L76">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M76">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="N76">
         <v>0</v>
@@ -5402,19 +4727,10 @@
         <v>1</v>
       </c>
       <c r="P76">
-        <v>0</v>
-      </c>
-      <c r="Q76">
-        <v>0</v>
-      </c>
-      <c r="R76">
-        <v>1</v>
-      </c>
-      <c r="S76">
         <v>75</v>
       </c>
     </row>
-    <row r="77" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>44013</v>
       </c>
@@ -5425,10 +4741,10 @@
         <v>640</v>
       </c>
       <c r="D77">
-        <v>616</v>
+        <v>1</v>
       </c>
       <c r="E77">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F77">
         <v>0</v>
@@ -5440,19 +4756,19 @@
         <v>0</v>
       </c>
       <c r="I77">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J77">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="K77">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="L77">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M77">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N77">
         <v>0</v>
@@ -5461,19 +4777,10 @@
         <v>1</v>
       </c>
       <c r="P77">
-        <v>0</v>
-      </c>
-      <c r="Q77">
-        <v>0</v>
-      </c>
-      <c r="R77">
-        <v>1</v>
-      </c>
-      <c r="S77">
         <v>76</v>
       </c>
     </row>
-    <row r="78" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>44044</v>
       </c>
@@ -5484,10 +4791,10 @@
         <v>605</v>
       </c>
       <c r="D78">
-        <v>640</v>
+        <v>1</v>
       </c>
       <c r="E78">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F78">
         <v>0</v>
@@ -5499,19 +4806,19 @@
         <v>0</v>
       </c>
       <c r="I78">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J78">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="K78">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="L78">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M78">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N78">
         <v>0</v>
@@ -5520,19 +4827,10 @@
         <v>1</v>
       </c>
       <c r="P78">
-        <v>0</v>
-      </c>
-      <c r="Q78">
-        <v>0</v>
-      </c>
-      <c r="R78">
-        <v>1</v>
-      </c>
-      <c r="S78">
         <v>77</v>
       </c>
     </row>
-    <row r="79" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>44075</v>
       </c>
@@ -5543,13 +4841,13 @@
         <v>623</v>
       </c>
       <c r="D79">
-        <v>605</v>
+        <v>1</v>
       </c>
       <c r="E79">
         <v>1</v>
       </c>
       <c r="F79">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G79">
         <v>0</v>
@@ -5558,40 +4856,31 @@
         <v>0</v>
       </c>
       <c r="I79">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="J79">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="K79">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="L79">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="M79">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N79">
         <v>0</v>
       </c>
       <c r="O79">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P79">
-        <v>1</v>
-      </c>
-      <c r="Q79">
-        <v>0</v>
-      </c>
-      <c r="R79">
-        <v>1</v>
-      </c>
-      <c r="S79">
         <v>78</v>
       </c>
     </row>
-    <row r="80" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>44105</v>
       </c>
@@ -5602,13 +4891,13 @@
         <v>705</v>
       </c>
       <c r="D80">
-        <v>623</v>
+        <v>1</v>
       </c>
       <c r="E80">
         <v>1</v>
       </c>
       <c r="F80">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G80">
         <v>0</v>
@@ -5617,40 +4906,31 @@
         <v>0</v>
       </c>
       <c r="I80">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J80">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="K80">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="L80">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="M80">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="N80">
         <v>0</v>
       </c>
       <c r="O80">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P80">
-        <v>1</v>
-      </c>
-      <c r="Q80">
-        <v>0</v>
-      </c>
-      <c r="R80">
-        <v>1</v>
-      </c>
-      <c r="S80">
         <v>79</v>
       </c>
     </row>
-    <row r="81" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>44136</v>
       </c>
@@ -5661,13 +4941,13 @@
         <v>626</v>
       </c>
       <c r="D81">
-        <v>705</v>
+        <v>1</v>
       </c>
       <c r="E81">
         <v>1</v>
       </c>
       <c r="F81">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G81">
         <v>0</v>
@@ -5676,40 +4956,31 @@
         <v>0</v>
       </c>
       <c r="I81">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="J81">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="K81">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="L81">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M81">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="N81">
         <v>0</v>
       </c>
       <c r="O81">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P81">
-        <v>1</v>
-      </c>
-      <c r="Q81">
-        <v>0</v>
-      </c>
-      <c r="R81">
-        <v>1</v>
-      </c>
-      <c r="S81">
         <v>80</v>
       </c>
     </row>
-    <row r="82" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>44166</v>
       </c>
@@ -5720,13 +4991,13 @@
         <v>615</v>
       </c>
       <c r="D82">
-        <v>626</v>
+        <v>1</v>
       </c>
       <c r="E82">
         <v>1</v>
       </c>
       <c r="F82">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G82">
         <v>0</v>
@@ -5735,40 +5006,31 @@
         <v>0</v>
       </c>
       <c r="I82">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="J82">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="K82">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="L82">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M82">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N82">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O82">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P82">
-        <v>0</v>
-      </c>
-      <c r="Q82">
-        <v>1</v>
-      </c>
-      <c r="R82">
-        <v>1</v>
-      </c>
-      <c r="S82">
         <v>81</v>
       </c>
     </row>
-    <row r="83" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>44197</v>
       </c>
@@ -5779,13 +5041,13 @@
         <v>654</v>
       </c>
       <c r="D83">
-        <v>615</v>
+        <v>1</v>
       </c>
       <c r="E83">
         <v>1</v>
       </c>
       <c r="F83">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G83">
         <v>0</v>
@@ -5794,40 +5056,31 @@
         <v>0</v>
       </c>
       <c r="I83">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="J83">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="K83">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="L83">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M83">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="N83">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O83">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P83">
-        <v>0</v>
-      </c>
-      <c r="Q83">
-        <v>1</v>
-      </c>
-      <c r="R83">
-        <v>1</v>
-      </c>
-      <c r="S83">
         <v>82</v>
       </c>
     </row>
-    <row r="84" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>44228</v>
       </c>
@@ -5838,13 +5091,13 @@
         <v>736</v>
       </c>
       <c r="D84">
-        <v>654</v>
+        <v>1</v>
       </c>
       <c r="E84">
         <v>1</v>
       </c>
       <c r="F84">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G84">
         <v>0</v>
@@ -5853,40 +5106,31 @@
         <v>0</v>
       </c>
       <c r="I84">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="J84">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="K84">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="L84">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M84">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N84">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O84">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P84">
-        <v>0</v>
-      </c>
-      <c r="Q84">
-        <v>1</v>
-      </c>
-      <c r="R84">
-        <v>1</v>
-      </c>
-      <c r="S84">
         <v>83</v>
       </c>
     </row>
-    <row r="85" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>44256</v>
       </c>
@@ -5897,13 +5141,13 @@
         <v>901</v>
       </c>
       <c r="D85">
-        <v>736</v>
+        <v>1</v>
       </c>
       <c r="E85">
         <v>1</v>
       </c>
       <c r="F85">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G85">
         <v>0</v>
@@ -5912,40 +5156,31 @@
         <v>0</v>
       </c>
       <c r="I85">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J85">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="K85">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="L85">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="M85">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="N85">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P85">
-        <v>0</v>
-      </c>
-      <c r="Q85">
-        <v>0</v>
-      </c>
-      <c r="R85">
-        <v>1</v>
-      </c>
-      <c r="S85">
         <v>84</v>
       </c>
     </row>
-    <row r="86" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>44287</v>
       </c>
@@ -5956,13 +5191,13 @@
         <v>710</v>
       </c>
       <c r="D86">
-        <v>901</v>
+        <v>1</v>
       </c>
       <c r="E86">
         <v>1</v>
       </c>
       <c r="F86">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G86">
         <v>0</v>
@@ -5971,40 +5206,31 @@
         <v>0</v>
       </c>
       <c r="I86">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="J86">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="K86">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="L86">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M86">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="N86">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P86">
-        <v>0</v>
-      </c>
-      <c r="Q86">
-        <v>0</v>
-      </c>
-      <c r="R86">
-        <v>1</v>
-      </c>
-      <c r="S86">
         <v>85</v>
       </c>
     </row>
-    <row r="87" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>44317</v>
       </c>
@@ -6015,13 +5241,13 @@
         <v>802</v>
       </c>
       <c r="D87">
-        <v>710</v>
+        <v>1</v>
       </c>
       <c r="E87">
         <v>1</v>
       </c>
       <c r="F87">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G87">
         <v>0</v>
@@ -6030,40 +5256,31 @@
         <v>0</v>
       </c>
       <c r="I87">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="J87">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="K87">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="L87">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M87">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N87">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P87">
-        <v>0</v>
-      </c>
-      <c r="Q87">
-        <v>0</v>
-      </c>
-      <c r="R87">
-        <v>1</v>
-      </c>
-      <c r="S87">
         <v>86</v>
       </c>
     </row>
-    <row r="88" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>44348</v>
       </c>
@@ -6074,13 +5291,13 @@
         <v>758</v>
       </c>
       <c r="D88">
-        <v>802</v>
+        <v>1</v>
       </c>
       <c r="E88">
         <v>1</v>
       </c>
       <c r="F88">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G88">
         <v>0</v>
@@ -6089,19 +5306,19 @@
         <v>0</v>
       </c>
       <c r="I88">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="J88">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="K88">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="L88">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="M88">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="N88">
         <v>0</v>
@@ -6110,19 +5327,10 @@
         <v>1</v>
       </c>
       <c r="P88">
-        <v>0</v>
-      </c>
-      <c r="Q88">
-        <v>0</v>
-      </c>
-      <c r="R88">
-        <v>1</v>
-      </c>
-      <c r="S88">
         <v>87</v>
       </c>
     </row>
-    <row r="89" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <v>44378</v>
       </c>
@@ -6133,13 +5341,13 @@
         <v>781</v>
       </c>
       <c r="D89">
-        <v>758</v>
+        <v>1</v>
       </c>
       <c r="E89">
         <v>1</v>
       </c>
       <c r="F89">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G89">
         <v>0</v>
@@ -6148,19 +5356,19 @@
         <v>0</v>
       </c>
       <c r="I89">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="J89">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="K89">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="L89">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="M89">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="N89">
         <v>0</v>
@@ -6169,19 +5377,10 @@
         <v>1</v>
       </c>
       <c r="P89">
-        <v>0</v>
-      </c>
-      <c r="Q89">
-        <v>0</v>
-      </c>
-      <c r="R89">
-        <v>1</v>
-      </c>
-      <c r="S89">
         <v>88</v>
       </c>
     </row>
-    <row r="90" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>44409</v>
       </c>
@@ -6192,13 +5391,13 @@
         <v>785</v>
       </c>
       <c r="D90">
-        <v>781</v>
+        <v>1</v>
       </c>
       <c r="E90">
         <v>1</v>
       </c>
       <c r="F90">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G90">
         <v>0</v>
@@ -6207,40 +5406,31 @@
         <v>0</v>
       </c>
       <c r="I90">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="J90">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="K90">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="L90">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="M90">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="N90">
         <v>0</v>
       </c>
       <c r="O90">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P90">
-        <v>0</v>
-      </c>
-      <c r="Q90">
-        <v>0</v>
-      </c>
-      <c r="R90">
-        <v>0</v>
-      </c>
-      <c r="S90">
         <v>89</v>
       </c>
     </row>
-    <row r="91" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>44440</v>
       </c>
@@ -6251,13 +5441,13 @@
         <v>680</v>
       </c>
       <c r="D91">
-        <v>785</v>
+        <v>1</v>
       </c>
       <c r="E91">
         <v>1</v>
       </c>
       <c r="F91">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G91">
         <v>0</v>
@@ -6266,19 +5456,19 @@
         <v>0</v>
       </c>
       <c r="I91">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="J91">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="K91">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="L91">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M91">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="N91">
         <v>0</v>
@@ -6287,19 +5477,10 @@
         <v>0</v>
       </c>
       <c r="P91">
-        <v>1</v>
-      </c>
-      <c r="Q91">
-        <v>0</v>
-      </c>
-      <c r="R91">
-        <v>0</v>
-      </c>
-      <c r="S91">
         <v>90</v>
       </c>
     </row>
-    <row r="92" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>44470</v>
       </c>
@@ -6310,13 +5491,13 @@
         <v>781</v>
       </c>
       <c r="D92">
-        <v>680</v>
+        <v>1</v>
       </c>
       <c r="E92">
         <v>1</v>
       </c>
       <c r="F92">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G92">
         <v>0</v>
@@ -6325,19 +5506,19 @@
         <v>0</v>
       </c>
       <c r="I92">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="J92">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="K92">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="L92">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="M92">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N92">
         <v>0</v>
@@ -6346,19 +5527,10 @@
         <v>0</v>
       </c>
       <c r="P92">
-        <v>1</v>
-      </c>
-      <c r="Q92">
-        <v>0</v>
-      </c>
-      <c r="R92">
-        <v>0</v>
-      </c>
-      <c r="S92">
         <v>91</v>
       </c>
     </row>
-    <row r="93" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>44501</v>
       </c>
@@ -6369,13 +5541,13 @@
         <v>741</v>
       </c>
       <c r="D93">
-        <v>781</v>
+        <v>1</v>
       </c>
       <c r="E93">
         <v>1</v>
       </c>
       <c r="F93">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G93">
         <v>0</v>
@@ -6384,19 +5556,19 @@
         <v>0</v>
       </c>
       <c r="I93">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J93">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="K93">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="L93">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M93">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="N93">
         <v>0</v>
@@ -6405,19 +5577,10 @@
         <v>0</v>
       </c>
       <c r="P93">
-        <v>1</v>
-      </c>
-      <c r="Q93">
-        <v>0</v>
-      </c>
-      <c r="R93">
-        <v>0</v>
-      </c>
-      <c r="S93">
         <v>92</v>
       </c>
     </row>
-    <row r="94" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <v>44531</v>
       </c>
@@ -6428,13 +5591,13 @@
         <v>660</v>
       </c>
       <c r="D94">
-        <v>741</v>
+        <v>1</v>
       </c>
       <c r="E94">
         <v>1</v>
       </c>
       <c r="F94">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G94">
         <v>0</v>
@@ -6443,40 +5606,31 @@
         <v>0</v>
       </c>
       <c r="I94">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="J94">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="K94">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L94">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M94">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O94">
         <v>0</v>
       </c>
       <c r="P94">
-        <v>0</v>
-      </c>
-      <c r="Q94">
-        <v>1</v>
-      </c>
-      <c r="R94">
-        <v>0</v>
-      </c>
-      <c r="S94">
         <v>93</v>
       </c>
     </row>
-    <row r="95" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>44562</v>
       </c>
@@ -6487,7 +5641,7 @@
         <v>684</v>
       </c>
       <c r="D95">
-        <v>660</v>
+        <v>1</v>
       </c>
       <c r="E95">
         <v>1</v>
@@ -6496,46 +5650,37 @@
         <v>1</v>
       </c>
       <c r="G95">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H95">
         <v>0</v>
       </c>
       <c r="I95">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="J95">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="K95">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="L95">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="M95">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="N95">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O95">
         <v>0</v>
       </c>
       <c r="P95">
-        <v>0</v>
-      </c>
-      <c r="Q95">
-        <v>1</v>
-      </c>
-      <c r="R95">
-        <v>0</v>
-      </c>
-      <c r="S95">
         <v>94</v>
       </c>
     </row>
-    <row r="96" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>44593</v>
       </c>
@@ -6546,7 +5691,7 @@
         <v>671</v>
       </c>
       <c r="D96">
-        <v>684</v>
+        <v>1</v>
       </c>
       <c r="E96">
         <v>1</v>
@@ -6558,43 +5703,34 @@
         <v>1</v>
       </c>
       <c r="H96">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I96">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="J96">
-        <v>36</v>
+        <v>93</v>
       </c>
       <c r="K96">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L96">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="M96">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="N96">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O96">
         <v>0</v>
       </c>
       <c r="P96">
-        <v>0</v>
-      </c>
-      <c r="Q96">
-        <v>1</v>
-      </c>
-      <c r="R96">
-        <v>0</v>
-      </c>
-      <c r="S96">
         <v>95</v>
       </c>
     </row>
-    <row r="97" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
         <v>44621</v>
       </c>
@@ -6605,7 +5741,7 @@
         <v>583</v>
       </c>
       <c r="D97">
-        <v>671</v>
+        <v>1</v>
       </c>
       <c r="E97">
         <v>1</v>
@@ -6620,40 +5756,31 @@
         <v>1</v>
       </c>
       <c r="I97">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="J97">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="K97">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="L97">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="M97">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="N97">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O97">
         <v>0</v>
       </c>
       <c r="P97">
-        <v>0</v>
-      </c>
-      <c r="Q97">
-        <v>0</v>
-      </c>
-      <c r="R97">
-        <v>0</v>
-      </c>
-      <c r="S97">
         <v>96</v>
       </c>
     </row>
-    <row r="98" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
         <v>44652</v>
       </c>
@@ -6664,7 +5791,7 @@
         <v>671</v>
       </c>
       <c r="D98">
-        <v>583</v>
+        <v>1</v>
       </c>
       <c r="E98">
         <v>1</v>
@@ -6679,40 +5806,31 @@
         <v>1</v>
       </c>
       <c r="I98">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="J98">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="K98">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="L98">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M98">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="N98">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O98">
         <v>0</v>
       </c>
       <c r="P98">
-        <v>0</v>
-      </c>
-      <c r="Q98">
-        <v>0</v>
-      </c>
-      <c r="R98">
-        <v>0</v>
-      </c>
-      <c r="S98">
         <v>97</v>
       </c>
     </row>
-    <row r="99" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
         <v>44682</v>
       </c>
@@ -6723,7 +5841,7 @@
         <v>767</v>
       </c>
       <c r="D99">
-        <v>671</v>
+        <v>1</v>
       </c>
       <c r="E99">
         <v>1</v>
@@ -6738,40 +5856,31 @@
         <v>1</v>
       </c>
       <c r="I99">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="J99">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="K99">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="L99">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M99">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="N99">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O99">
         <v>0</v>
       </c>
       <c r="P99">
-        <v>0</v>
-      </c>
-      <c r="Q99">
-        <v>0</v>
-      </c>
-      <c r="R99">
-        <v>0</v>
-      </c>
-      <c r="S99">
         <v>98</v>
       </c>
     </row>
-    <row r="100" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
         <v>44713</v>
       </c>
@@ -6782,7 +5891,7 @@
         <v>668</v>
       </c>
       <c r="D100">
-        <v>767</v>
+        <v>1</v>
       </c>
       <c r="E100">
         <v>1</v>
@@ -6797,40 +5906,31 @@
         <v>1</v>
       </c>
       <c r="I100">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="J100">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="K100">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="L100">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M100">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N100">
         <v>0</v>
       </c>
       <c r="O100">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P100">
-        <v>0</v>
-      </c>
-      <c r="Q100">
-        <v>0</v>
-      </c>
-      <c r="R100">
-        <v>0</v>
-      </c>
-      <c r="S100">
         <v>99</v>
       </c>
     </row>
-    <row r="101" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
         <v>44743</v>
       </c>
@@ -6841,7 +5941,7 @@
         <v>656</v>
       </c>
       <c r="D101">
-        <v>668</v>
+        <v>1</v>
       </c>
       <c r="E101">
         <v>1</v>
@@ -6856,40 +5956,31 @@
         <v>1</v>
       </c>
       <c r="I101">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="J101">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="K101">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L101">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="M101">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N101">
         <v>0</v>
       </c>
       <c r="O101">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P101">
-        <v>0</v>
-      </c>
-      <c r="Q101">
-        <v>0</v>
-      </c>
-      <c r="R101">
-        <v>0</v>
-      </c>
-      <c r="S101">
         <v>100</v>
       </c>
     </row>
-    <row r="102" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
         <v>44774</v>
       </c>
@@ -6900,7 +5991,7 @@
         <v>662</v>
       </c>
       <c r="D102">
-        <v>656</v>
+        <v>1</v>
       </c>
       <c r="E102">
         <v>1</v>
@@ -6915,40 +6006,31 @@
         <v>1</v>
       </c>
       <c r="I102">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="J102">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="K102">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="L102">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M102">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="N102">
         <v>0</v>
       </c>
       <c r="O102">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P102">
-        <v>0</v>
-      </c>
-      <c r="Q102">
-        <v>0</v>
-      </c>
-      <c r="R102">
-        <v>0</v>
-      </c>
-      <c r="S102">
         <v>101</v>
       </c>
     </row>
-    <row r="103" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
         <v>44805</v>
       </c>
@@ -6959,7 +6041,7 @@
         <v>662</v>
       </c>
       <c r="D103">
-        <v>662</v>
+        <v>1</v>
       </c>
       <c r="E103">
         <v>1</v>
@@ -6974,19 +6056,19 @@
         <v>1</v>
       </c>
       <c r="I103">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="J103">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="K103">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="L103">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M103">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N103">
         <v>0</v>
@@ -6995,19 +6077,10 @@
         <v>0</v>
       </c>
       <c r="P103">
-        <v>1</v>
-      </c>
-      <c r="Q103">
-        <v>0</v>
-      </c>
-      <c r="R103">
-        <v>0</v>
-      </c>
-      <c r="S103">
         <v>102</v>
       </c>
     </row>
-    <row r="104" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
         <v>44835</v>
       </c>
@@ -7018,7 +6091,7 @@
         <v>662</v>
       </c>
       <c r="D104">
-        <v>662</v>
+        <v>1</v>
       </c>
       <c r="E104">
         <v>1</v>
@@ -7033,19 +6106,19 @@
         <v>1</v>
       </c>
       <c r="I104">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="J104">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K104">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="L104">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="M104">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N104">
         <v>0</v>
@@ -7054,19 +6127,10 @@
         <v>0</v>
       </c>
       <c r="P104">
-        <v>1</v>
-      </c>
-      <c r="Q104">
-        <v>0</v>
-      </c>
-      <c r="R104">
-        <v>0</v>
-      </c>
-      <c r="S104">
         <v>103</v>
       </c>
     </row>
-    <row r="105" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
         <v>44866</v>
       </c>
@@ -7077,7 +6141,7 @@
         <v>636</v>
       </c>
       <c r="D105">
-        <v>662</v>
+        <v>1</v>
       </c>
       <c r="E105">
         <v>1</v>
@@ -7092,19 +6156,19 @@
         <v>1</v>
       </c>
       <c r="I105">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="J105">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="K105">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="L105">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M105">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="N105">
         <v>0</v>
@@ -7113,19 +6177,10 @@
         <v>0</v>
       </c>
       <c r="P105">
-        <v>1</v>
-      </c>
-      <c r="Q105">
-        <v>0</v>
-      </c>
-      <c r="R105">
-        <v>0</v>
-      </c>
-      <c r="S105">
         <v>104</v>
       </c>
     </row>
-    <row r="106" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
         <v>44896</v>
       </c>
@@ -7136,7 +6191,7 @@
         <v>616</v>
       </c>
       <c r="D106">
-        <v>636</v>
+        <v>1</v>
       </c>
       <c r="E106">
         <v>1</v>
@@ -7151,40 +6206,31 @@
         <v>1</v>
       </c>
       <c r="I106">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="J106">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="K106">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="L106">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M106">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N106">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O106">
         <v>0</v>
       </c>
       <c r="P106">
-        <v>0</v>
-      </c>
-      <c r="Q106">
-        <v>1</v>
-      </c>
-      <c r="R106">
-        <v>0</v>
-      </c>
-      <c r="S106">
         <v>105</v>
       </c>
     </row>
-    <row r="107" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
         <v>44927</v>
       </c>
@@ -7195,7 +6241,7 @@
         <v>686</v>
       </c>
       <c r="D107">
-        <v>616</v>
+        <v>1</v>
       </c>
       <c r="E107">
         <v>1</v>
@@ -7210,40 +6256,31 @@
         <v>1</v>
       </c>
       <c r="I107">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="J107">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="K107">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="L107">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M107">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N107">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O107">
         <v>0</v>
       </c>
       <c r="P107">
-        <v>0</v>
-      </c>
-      <c r="Q107">
-        <v>1</v>
-      </c>
-      <c r="R107">
-        <v>0</v>
-      </c>
-      <c r="S107">
         <v>106</v>
       </c>
     </row>
-    <row r="108" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
         <v>44958</v>
       </c>
@@ -7254,7 +6291,7 @@
         <v>594</v>
       </c>
       <c r="D108">
-        <v>686</v>
+        <v>1</v>
       </c>
       <c r="E108">
         <v>1</v>
@@ -7269,40 +6306,31 @@
         <v>1</v>
       </c>
       <c r="I108">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="J108">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="K108">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="L108">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M108">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="N108">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O108">
         <v>0</v>
       </c>
       <c r="P108">
-        <v>0</v>
-      </c>
-      <c r="Q108">
-        <v>1</v>
-      </c>
-      <c r="R108">
-        <v>0</v>
-      </c>
-      <c r="S108">
         <v>107</v>
       </c>
     </row>
-    <row r="109" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
         <v>44986</v>
       </c>
@@ -7313,7 +6341,7 @@
         <v>774</v>
       </c>
       <c r="D109">
-        <v>594</v>
+        <v>1</v>
       </c>
       <c r="E109">
         <v>1</v>
@@ -7328,40 +6356,31 @@
         <v>1</v>
       </c>
       <c r="I109">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="J109">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="K109">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="L109">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="M109">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="N109">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O109">
         <v>0</v>
       </c>
       <c r="P109">
-        <v>0</v>
-      </c>
-      <c r="Q109">
-        <v>0</v>
-      </c>
-      <c r="R109">
-        <v>0</v>
-      </c>
-      <c r="S109">
         <v>108</v>
       </c>
     </row>
-    <row r="110" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
         <v>45017</v>
       </c>
@@ -7372,7 +6391,7 @@
         <v>642</v>
       </c>
       <c r="D110">
-        <v>774</v>
+        <v>1</v>
       </c>
       <c r="E110">
         <v>1</v>
@@ -7387,40 +6406,31 @@
         <v>1</v>
       </c>
       <c r="I110">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="J110">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="K110">
-        <v>47</v>
+        <v>1</v>
       </c>
       <c r="L110">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M110">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="N110">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O110">
         <v>0</v>
       </c>
       <c r="P110">
-        <v>0</v>
-      </c>
-      <c r="Q110">
-        <v>0</v>
-      </c>
-      <c r="R110">
-        <v>0</v>
-      </c>
-      <c r="S110">
         <v>109</v>
       </c>
     </row>
-    <row r="111" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
         <v>45047</v>
       </c>
@@ -7431,7 +6441,7 @@
         <v>657</v>
       </c>
       <c r="D111">
-        <v>642</v>
+        <v>1</v>
       </c>
       <c r="E111">
         <v>1</v>
@@ -7446,40 +6456,31 @@
         <v>1</v>
       </c>
       <c r="I111">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="J111">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="K111">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="L111">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M111">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N111">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O111">
         <v>0</v>
       </c>
       <c r="P111">
-        <v>0</v>
-      </c>
-      <c r="Q111">
-        <v>0</v>
-      </c>
-      <c r="R111">
-        <v>0</v>
-      </c>
-      <c r="S111">
         <v>110</v>
       </c>
     </row>
-    <row r="112" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
         <v>45078</v>
       </c>
@@ -7490,7 +6491,7 @@
         <v>756</v>
       </c>
       <c r="D112">
-        <v>657</v>
+        <v>1</v>
       </c>
       <c r="E112">
         <v>1</v>
@@ -7505,40 +6506,31 @@
         <v>1</v>
       </c>
       <c r="I112">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="J112">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="K112">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="L112">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M112">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="N112">
         <v>0</v>
       </c>
       <c r="O112">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P112">
-        <v>0</v>
-      </c>
-      <c r="Q112">
-        <v>0</v>
-      </c>
-      <c r="R112">
-        <v>0</v>
-      </c>
-      <c r="S112">
         <v>111</v>
       </c>
     </row>
-    <row r="113" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
         <v>45108</v>
       </c>
@@ -7549,7 +6541,7 @@
         <v>830</v>
       </c>
       <c r="D113">
-        <v>756</v>
+        <v>1</v>
       </c>
       <c r="E113">
         <v>1</v>
@@ -7564,40 +6556,31 @@
         <v>1</v>
       </c>
       <c r="I113">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="J113">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="K113">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="L113">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="M113">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N113">
         <v>0</v>
       </c>
       <c r="O113">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P113">
-        <v>0</v>
-      </c>
-      <c r="Q113">
-        <v>0</v>
-      </c>
-      <c r="R113">
-        <v>0</v>
-      </c>
-      <c r="S113">
         <v>112</v>
       </c>
     </row>
-    <row r="114" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
         <v>45139</v>
       </c>
@@ -7608,7 +6591,7 @@
         <v>867</v>
       </c>
       <c r="D114">
-        <v>830</v>
+        <v>1</v>
       </c>
       <c r="E114">
         <v>1</v>
@@ -7623,40 +6606,31 @@
         <v>1</v>
       </c>
       <c r="I114">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="J114">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="K114">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="L114">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="M114">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="N114">
         <v>0</v>
       </c>
       <c r="O114">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P114">
-        <v>0</v>
-      </c>
-      <c r="Q114">
-        <v>0</v>
-      </c>
-      <c r="R114">
-        <v>0</v>
-      </c>
-      <c r="S114">
         <v>113</v>
       </c>
     </row>
-    <row r="115" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
         <v>45170</v>
       </c>
@@ -7667,7 +6641,7 @@
         <v>686</v>
       </c>
       <c r="D115">
-        <v>867</v>
+        <v>1</v>
       </c>
       <c r="E115">
         <v>1</v>
@@ -7682,19 +6656,19 @@
         <v>1</v>
       </c>
       <c r="I115">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="J115">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="K115">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="L115">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M115">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N115">
         <v>0</v>
@@ -7703,19 +6677,10 @@
         <v>0</v>
       </c>
       <c r="P115">
-        <v>1</v>
-      </c>
-      <c r="Q115">
-        <v>0</v>
-      </c>
-      <c r="R115">
-        <v>0</v>
-      </c>
-      <c r="S115">
         <v>114</v>
       </c>
     </row>
-    <row r="116" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
         <v>45200</v>
       </c>
@@ -7726,7 +6691,7 @@
         <v>759</v>
       </c>
       <c r="D116">
-        <v>686</v>
+        <v>1</v>
       </c>
       <c r="E116">
         <v>1</v>
@@ -7741,19 +6706,19 @@
         <v>1</v>
       </c>
       <c r="I116">
-        <v>1</v>
+        <v>53</v>
       </c>
       <c r="J116">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="K116">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="L116">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="M116">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N116">
         <v>0</v>
@@ -7762,19 +6727,10 @@
         <v>0</v>
       </c>
       <c r="P116">
-        <v>1</v>
-      </c>
-      <c r="Q116">
-        <v>0</v>
-      </c>
-      <c r="R116">
-        <v>0</v>
-      </c>
-      <c r="S116">
         <v>115</v>
       </c>
     </row>
-    <row r="117" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
         <v>45231</v>
       </c>
@@ -7785,7 +6741,7 @@
         <v>695</v>
       </c>
       <c r="D117">
-        <v>759</v>
+        <v>1</v>
       </c>
       <c r="E117">
         <v>1</v>
@@ -7800,19 +6756,19 @@
         <v>1</v>
       </c>
       <c r="I117">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="J117">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="K117">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="L117">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M117">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="N117">
         <v>0</v>
@@ -7821,19 +6777,10 @@
         <v>0</v>
       </c>
       <c r="P117">
-        <v>1</v>
-      </c>
-      <c r="Q117">
-        <v>0</v>
-      </c>
-      <c r="R117">
-        <v>0</v>
-      </c>
-      <c r="S117">
         <v>116</v>
       </c>
     </row>
-    <row r="118" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
         <v>45261</v>
       </c>
@@ -7844,7 +6791,7 @@
         <v>662</v>
       </c>
       <c r="D118">
-        <v>695</v>
+        <v>1</v>
       </c>
       <c r="E118">
         <v>1</v>
@@ -7859,40 +6806,31 @@
         <v>1</v>
       </c>
       <c r="I118">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="J118">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="K118">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="L118">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="M118">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="N118">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O118">
         <v>0</v>
       </c>
       <c r="P118">
-        <v>0</v>
-      </c>
-      <c r="Q118">
-        <v>1</v>
-      </c>
-      <c r="R118">
-        <v>0</v>
-      </c>
-      <c r="S118">
         <v>117</v>
       </c>
     </row>
-    <row r="119" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
         <v>45292</v>
       </c>
@@ -7903,7 +6841,7 @@
         <v>743</v>
       </c>
       <c r="D119">
-        <v>662</v>
+        <v>1</v>
       </c>
       <c r="E119">
         <v>1</v>
@@ -7918,36 +6856,27 @@
         <v>1</v>
       </c>
       <c r="I119">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="J119">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="K119">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="L119">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="M119">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="N119">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O119">
         <v>0</v>
       </c>
       <c r="P119">
-        <v>0</v>
-      </c>
-      <c r="Q119">
-        <v>1</v>
-      </c>
-      <c r="R119">
-        <v>0</v>
-      </c>
-      <c r="S119">
         <v>118</v>
       </c>
     </row>
